--- a/docs/StructureDefinition-MedicationRequestNonVAMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVAMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVAMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVAMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVAMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVAMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestNonVAMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestNonVAMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA NON (file 55.05) to FHIR MedicationRequest</t>
+    <t>This StructureDefinition contains the maps for VistA file NON (#55.05) to us-core-medicationrequest</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -596,7 +596,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-18:1540: fixed value = plan if NON-VA MEDS - ORDER NUMBER (#55.05-7) case Not null {null}</t>
+inv-18:1540: fixed value = plan when NON-VA MEDS - ORDER NUMBER (#55.05-7) case Not null {null}</t>
   </si>
   <si>
     <t>Request.intent</t>
@@ -608,7 +608,7 @@
     <t>FiveWs.class</t>
   </si>
   <si>
-    <t>1540: fixed value = plan if NON-VA MEDS - ORDER NUMBER (#55.05-7) case Not null</t>
+    <t>1540: fixed value = plan when NON-VA MEDS - ORDER NUMBER (#55.05-7) case Not null</t>
   </si>
   <si>
     <t>MedicationRequest.category</t>
@@ -725,10 +725,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-19:1347: fixed value = true if NON-VA MEDS - ORDER NUMBER (#55.05-7) case Not null {null}</t>
-  </si>
-  <si>
-    <t>1347: fixed value = true if NON-VA MEDS - ORDER NUMBER (#55.05-7) case Not null</t>
+inv-19:1347: fixed value = true when NON-VA MEDS - ORDER NUMBER (#55.05-7) case Not null {null}</t>
+  </si>
+  <si>
+    <t>1347: fixed value = true when NON-VA MEDS - ORDER NUMBER (#55.05-7) case Not null</t>
   </si>
   <si>
     <t>MedicationRequest.medication[x]</t>
